--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,42 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Customer Solution Architect — Arango AI Product Suite</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>ARANGO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Azure Databricks Architect Healthcare Payer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5652d49391bd82a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>J&amp;T Business Consulting</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Annapolis Junction, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Hadoop, Spark, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439377efddb3496b</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, New College Graduate,</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>North Reading, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a9c723d1fa4a196</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Enterprise Architect Integration Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dbb073f20120e13</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea23a7afe82982</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c9dc97e7a8c55</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97ef6349d26627c1</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Product Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Diaconia, LLC.</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, Oracle, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed19f7417f9c2e59</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,94 +2526,94 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e9b523a42f1787</t>
+          <t>https://www.indeed.com/viewjob?jk=7024b9745320678f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Support Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b138daabe966037</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01c677c253d655bb</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Architect - Public Sector (SLED)</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ubiety</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Unum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a647a34b37a72a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,242 +3331,242 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Datawarehouse Architect for New York City NY</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Centillion Infotech LLC</t>
+          <t>Ubiety</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, Python, SQL</t>
+          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11b6e886c2b743d</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,129 +3611,129 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,17 +3846,472 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Advanced Specialist, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Software Engineer II - MCP Development</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Platform Engineer, Data Services</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vytalize Health</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Integres, LLC</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
           <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Rhodes Financial Services</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Evans, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>North Augusta, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Aiken, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Grovetown, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Onebridge</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -818,35 +818,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Customer Solution Architect — Arango AI Product Suite</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ARANGO</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=632508141e5e7e23</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Senior Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Native Developer- EST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Enterprise Architect Integration Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1063ffb870d53611</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Revenue Management Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=7024b9745320678f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7024b9745320678f</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III (Java/Spring/SQL)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
         </is>
       </c>
     </row>
@@ -3758,17 +3758,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4413ec7a4b00d4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e48a5b4af545b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Advanced Specialist, Data Engineering</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7567cb365890dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - ITS4</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1054e208948fd6fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
@@ -1413,25 +1413,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Native Developer- EST</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37e94025d78d00b3</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Enterprise Architect Integration Engineer II</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Senior Snowflake Platform Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Groton, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=786fbdb63698b11b</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Revenue Management Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7024b9745320678f</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring/SQL)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, dbt, MLOps, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Software Engineer III (Java/Spring/SQL)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Techfield</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Mindex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Architect - Public Sector (SLED)</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d898f82946c9db3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Public Sector (SLED)</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deaebb012d17a528</t>
+          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ubiety</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, GCP, Scala, Kafka, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd4531981abb3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
         </is>
       </c>
     </row>
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Full Stack .NET Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Enlyte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=47735df267dc44af</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,69 +3706,69 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Vinik Sports Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Advanced Specialist, Data Engineering</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,85 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Onebridge</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Snowflake Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Groton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Time Travel, clustering keys, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ad590ea8a95921</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Data Modeling, ETL, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df567011cf662897</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Science Analyst - Agentic AI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Revenue Management Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior AI Engineer / AI Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
         </is>
       </c>
     </row>
@@ -3618,17 +3618,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,69 +3741,69 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vinik Sports Group</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Vinik Sports Group</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Advanced Specialist, Data Engineering</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,15 +4371,50 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Security Automation Engineer (Python)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Onebridge</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
+          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architect Integration Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Data Platform &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Indigenous Pact PBC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Science Analyst - Agentic AI Developer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Vertex AI, Spark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70aff22bb7641b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>Revenue Management Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,112 +2446,112 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,147 +2666,147 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, dbt, MLOps, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring/SQL)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
         </is>
       </c>
     </row>
@@ -2818,30 +2818,30 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
         </is>
       </c>
     </row>
@@ -2853,615 +2853,615 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Techfield</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, Hive, Spark, Scala, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95557e0528468ca2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329cdc7ca8132e90</t>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a4ebf0e5f5c11c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c6a06a8d28780bf</t>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (Azure &amp; Snowflake) - Remote</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mindex</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd6304cc9580794e</t>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45dbfc4cd100a9e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6af3bda05e023a</t>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69c77cc5b5195f78</t>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Engineer / AI Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,147 +3576,147 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9091b30f2387d253</t>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior Full Stack .NET Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47735df267dc44af</t>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
         </is>
       </c>
     </row>
@@ -3728,440 +3728,440 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Vinik Sports Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>North Augusta, SC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Aiken, SC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Grovetown, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,40 +4381,3295 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>University of Idaho</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Moscow, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>WY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SD, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>NM, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>NH, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>NE, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>VT, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MS, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DE, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MO, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>WI, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AR, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ND, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>OK, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>MN, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CT, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SC, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>ID, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>LA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>WV, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Total Wine &amp; More</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Expleo Group</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Littleton, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, dbt, MLOps, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Marathon Health</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Pearl City, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Marathon Health</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pearl City, HI, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Java/Spring/SQL)</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Master Data Management (MDM) Data Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>American Association of Insurance Services</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Data Engineer, Senior (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Releady</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Data Engineer, Senior</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Releady</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Reporting Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Wpromote, LLC</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sr Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Lennar</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>DBHDS - SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Betis Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Managing Engineer – (Software Development/Container Workloads)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, ELT, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bebc36460aaeb195</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>CalAmp</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Senior Security Architect(AI)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Paylocity</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Junior Full Stack .NET Developer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Enlyte</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47735df267dc44af</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nashville Predators</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Unity Technologies</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Micron Technology</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Deltek</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>We Write Code</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Dell Technologies</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Fooda</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Vinik Sports Group</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Software Architect – Manufacturing Test</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Advanced Specialist, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Bloomington, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Software Engineer II - MCP Development</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Platform Engineer, Data Services</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Vytalize Health</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Database Developer</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Integres, LLC</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Rhodes Financial Services</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Evans, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>North Augusta, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Augusta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Aiken, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>TaxSlayer</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Grovetown, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Onebridge</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D207" t="n">
         <v>10.4</v>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G207" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G207"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Scicom Infrastructure Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
+          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>[C] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=623cec7f1ca0a4a6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Software Engineer III - Risk Decision Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Enterprise Architect Integration Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,59 +1861,59 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8deaa38cca423e7</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
@@ -2218,25 +2218,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Revenue Management Solutions</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a966c05563f98c</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b02e7a9293c05e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,67 +4171,67 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Mastronardi Produce</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, dbt, MLOps, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ccee570c0b2629</t>
+          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Software Engineer III (Java/Spring/SQL)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,102 +6271,102 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring/SQL)</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0b237d7cb0a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,17 +6611,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
@@ -6663,17 +6663,17 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Unity Technologies</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Full-Stack AI Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Junior Full Stack .NET Developer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Enlyte</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,77 +6821,77 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47735df267dc44af</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,129 +6901,129 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Vinik Sports Group</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,24 +7031,24 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Vinik Sports Group</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,34 +7171,34 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Advanced Specialist, Data Engineering</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Integres, LLC</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d1ad3be6df1730a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Evans, GA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -7321,24 +7321,24 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>North Augusta, SC, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Integres, LLC</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
+          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
         </is>
       </c>
     </row>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>TaxSlayer</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Aiken, SC, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Grovetown, GA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
+          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>TaxSlayer</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Evans, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,190 +7486,15 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>North Augusta, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Aiken, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Grovetown, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a0c773ba869ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33143989f3362efb</t>
+          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer II - Meter Data Management Software (Full Stack, Databricks)</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake Saint Louis, MO, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b784c8205aa1d58</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
         </is>
       </c>
     </row>
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Ops / DevOps Engineer</t>
+          <t>[C] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
+          <t>https://www.indeed.com/viewjob?jk=623cec7f1ca0a4a6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[C] Data Engineer, Safeguards</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623cec7f1ca0a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Cloud Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Data Engineer (Backend Python Development)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>Green Courte Residential Holdings</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Polars, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
+          <t>https://www.indeed.com/viewjob?jk=8581636bcd3b21c7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Risk Decision Technology</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, GCP, BigQuery, Dataflow, Hadoop, Hive, HBase, Kafka</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cecf643a53b2209</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Senior AWS Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Enterprise Integration Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Architect Integration Engineer II</t>
+          <t>Senior AI Security Automation Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Fairlife, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,104 +1816,104 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>AI Native, Tech Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>ConsumerAffairs</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1649dc6e6d00bbb</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4211cb353fe7a94e</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f9b2c310f5bfa3</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform &amp; Analytics Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Indigenous Pact PBC</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,129 +2106,129 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f8c703d51d3a40</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>AWS Devops Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,24 +2306,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,112 +3951,112 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,129 +4066,129 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist - Data Engineering</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, SQL Server, ETL, Tableau, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c8d9fe21fbf89b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Mastronardi Produce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fa1ca8e2ddf6df8</t>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,34 +5911,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Pearl City, HI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,137 +5991,137 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,32 +6131,32 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Reporting Solutions Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Wpromote, LLC</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,102 +6166,102 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DBHDS - SQL Database Administrator</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Betis Group, Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Managing Engineer – (Software Development/Container Workloads)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
+          <t>https://www.indeed.com/viewjob?jk=bebc36460aaeb195</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/Spring/SQL)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acea18330940b12</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>We Write Code</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,77 +6471,77 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,32 +6551,32 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,137 +6586,137 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Managing Engineer – (Software Development/Container Workloads)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Vinik Sports Group</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, ELT, Kubernetes</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebc36460aaeb195</t>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Unity Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,129 +6726,129 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=652b63d35a6266a3</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2b319c05d2be3e</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Hunt Valley, MD, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Platform Engineer, Data Services</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Rhodes Financial Services</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
+          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Security Automation Engineer (Python)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Onebridge</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,610 +6891,15 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Fooda</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Vinik Sports Group</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Software Architect – Manufacturing Test</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Cerebras Systems</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Software Engineer II - MCP Development</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Kiewit Corporation</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Contract Associate Development Engineer</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Sinclair Broadcast Group</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Hunt Valley, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Platform Engineer, Data Services</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Vytalize Health</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>KS, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Database Developer</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Integres, LLC</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, PySpark, SQL Server, Data Modeling, ETL, Power BI, Jenkins, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc8d97653729dfa4</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Rhodes Financial Services</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e38ede1f1c848056</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Evans, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cec52a87c2914b</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>North Augusta, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f84a2d5bc189bc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Augusta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9540e403cb0fe0bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Aiken, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39572bc0cbf1e1ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Software Developer</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TaxSlayer</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Grovetown, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f96379913f2a0b13</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Security Automation Engineer (Python)</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Onebridge</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
         </is>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer / Business Analyst – Data Contracts &amp; OCDS</t>
+          <t>Senior Software Engineer - 2378720</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da10e92c3ddc831a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>21.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, HDFS, MapReduce, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8438fc0eeeabc119</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior DevOps Engineer (NOAA badge required)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Element 84</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
+          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Microservices Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e170e5d541b6f7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>.Net Engineer-Data Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1916ff73e89dbf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Senior Analytics Engineer (AI Insurance SaaS)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>Redshift, RDS, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f178ece3a91c11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Cloud Data Engineer II</t>
+          <t>Data Engineer (Backend Python Development)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Green Courte Residential Holdings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Hadoop, Spark, Scala</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Polars, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4ff42758b01e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8581636bcd3b21c7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (Backend Python Development)</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Green Courte Residential Holdings</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Polars, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8581636bcd3b21c7</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Integration Engineer II</t>
+          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Benzinga</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba77f8c3e7eac143</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Security Automation Engineer</t>
+          <t>Enterprise Integration Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,59 +1791,59 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1acc92079f390921</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Native, Tech Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fairlife, LLC</t>
+          <t>ConsumerAffairs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34038fa38ced9dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Native, Tech Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ConsumerAffairs</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
         </is>
       </c>
     </row>
@@ -2008,25 +2008,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Devops Cloud Engineer</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b690190bc20de39</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
+          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
+          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,52 +3916,52 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>University of Idaho</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Moscow, ID, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Solutions Architect - Financial Services (Fintech / Data Providers)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=cfda330d88e5394e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Microsoft Data &amp; AI Services Solution Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MCAConnect</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Event Hubs, Hadoop, Spark, Scala, Kafka, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f08ca180466ecf65</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer, MTS, Enterprise Security, Identity &amp; Access Management</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08079db08d267e47</t>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,104 +5911,104 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20a0e05716125fb7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Pearl City, HI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c02a271654e63003</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Tewksbury, MA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Redshift, Hadoop, Scala, DynamoDB, Cassandra, ETL, ELT, CloudWatch</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=e937495306ed591b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Reporting Solutions Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wpromote, LLC</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cad2ebf6af99a7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DBHDS - SQL Database Administrator</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Betis Group, Inc.</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b671e1c355c84c5</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Managing Engineer – (Software Development/Container Workloads)</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, ELT, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebc36460aaeb195</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,17 +6296,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
@@ -6348,60 +6348,60 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,94 +6411,94 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Vinik Sports Group</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>We Write Code</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, Azure, Snowflake, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821497679584e2d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a8591136d286e</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
+          <t>https://www.indeed.com/viewjob?jk=69be0bf694e2c4f3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=10660dc7b9459d79</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,29 +6576,29 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=81fada79a0fdb321</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6611,34 +6611,34 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=4359bfbc2f710789</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vinik Sports Group</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+          <t>https://www.indeed.com/viewjob?jk=993ef220ab5ba1b7</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bec0ebeeca3759</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Sr. Solutions Architect - Digital Native Business, Strategics</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=905e4e31b6a4eb13</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Rhodes Financial Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, SQL Server, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291d753a3842da49</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec4d249ca819f87</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Security Automation Engineer (Python)</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Onebridge</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,17 +6891,122 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b78cc285cf07730</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Software Engineer II - MCP Development</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Platform Engineer, Data Services</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Vytalize Health</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>KS, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Operations Specialist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Scicom Infrastructure Services</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.5</v>
+        <v>25.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, S3, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63447d1670f0092</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf953a2c9ee5bf5</t>
         </is>
       </c>
     </row>
@@ -531,112 +531,112 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf953a2c9ee5bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc6276c79dcfd60</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - 2378720</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25.7</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc6276c79dcfd60</t>
+          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2378720</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Java Backend Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>Otomeshan technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=05dceb327eaee169</t>
         </is>
       </c>
     </row>
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Conduit services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1b649e399da37</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c782baa6dabb867</t>
+          <t>https://www.indeed.com/viewjob?jk=4981bd5c543f4424</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377853022880bb36</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2003e26eeb22b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4e902c4bf7accf</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>SANTEE COOPER</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Moncks Corner, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5384d191c57a074d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (NOAA badge required)</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Element 84</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, API Gateway, RDS, Azure, Databricks, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=034929104db4d3fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[C] Data Engineer, Safeguards</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623cec7f1ca0a4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=87068c1cc4a7e538</t>
         </is>
       </c>
     </row>
@@ -1203,52 +1203,52 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c3da01dbb88956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Research Engineer II - ML Ops</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f950c716669dfe8d</t>
+          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>.Net Engineer-Data Engineering</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Scala, Snowflake, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90c0e5d8f944baf1</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Texas Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
+          <t>https://www.indeed.com/viewjob?jk=3aada6e7b7a0a352</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>University Federal Credit Union</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cfb563279695cc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>Senior AI Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Neo4j</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ELT, CI/CD, Azure DevOps, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baa14defff29cc46</t>
+          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Software Developer II (Mid-level, Full-stack)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Science Systems and Applications, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
+          <t>https://www.indeed.com/viewjob?jk=f769425f85072466</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
+          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer – AI Applications</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>University of Idaho</t>
+          <t>Mears Group Inc</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Moscow, ID, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Databricks Lakehouse, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2714c15bcc60033</t>
+          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=08a0f24c148c6273</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Fintech / Data Providers)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfda330d88e5394e</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Microsoft Data &amp; AI Services Solution Architect</t>
+          <t>Sr. Solutions Architect - Financial Services (Fintech / Data Providers)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MCAConnect</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Hadoop, Spark, Scala, Kafka, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08ca180466ecf65</t>
+          <t>https://www.indeed.com/viewjob?jk=cfda330d88e5394e</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Microsoft Data &amp; AI Services Solution Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>MCAConnect</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Azure, Event Hubs, Hadoop, Spark, Scala, Kafka, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=f08ca180466ecf65</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,59 +5921,59 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,14 +5991,14 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tewksbury, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,34 +6121,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Hadoop, Scala, DynamoDB, Cassandra, ETL, ELT, CloudWatch</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937495306ed591b</t>
+          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=f34e5f97d02e5021</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=853d0155af0fe88a</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=025149537375b19e</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>Senior Software Engineer II- Streaming and Durability</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,34 +6261,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2aaa5458d436295c</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,34 +6296,34 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4086a87728e295</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Senior Software Engineer II- Streaming and Durability</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,297 +6331,297 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=e37397e5a5a0fd15</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
+          <t>IT Solutions Architect III</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1b2254b13ddb4d</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Fooda</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tewksbury, MA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
+          <t>AWS, Lambda, Redshift, Hadoop, Scala, DynamoDB, Cassandra, ETL, ELT, CloudWatch</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+          <t>https://www.indeed.com/viewjob?jk=e937495306ed591b</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Vinik Sports Group</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Data Modeling, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d085c6d211bbf396</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a8591136d286e</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69be0bf694e2c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10660dc7b9459d79</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fada79a0fdb321</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4359bfbc2f710789</t>
+          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=993ef220ab5ba1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a8591136d286e</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bec0ebeeca3759</t>
+          <t>https://www.indeed.com/viewjob?jk=69be0bf694e2c4f3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Solutions Architect - AI</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
+          <t>https://www.indeed.com/viewjob?jk=10660dc7b9459d79</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,24 +6751,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
+          <t>https://www.indeed.com/viewjob?jk=81fada79a0fdb321</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Digital Native Business, Strategics</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=905e4e31b6a4eb13</t>
+          <t>https://www.indeed.com/viewjob?jk=4359bfbc2f710789</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Software Architect – Manufacturing Test</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,14 +6831,14 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+          <t>https://www.indeed.com/viewjob?jk=993ef220ab5ba1b7</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec4d249ca819f87</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bec0ebeeca3759</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Software Engineer II - MCP Development</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hunt Valley, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Platform Engineer, Data Services</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Databricks, GCP, Scala, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,7 +7006,322 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00036ac2c3d4f673</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ec4d249ca819f87</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Boston Scientific</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Marlboro, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23d224fc86dd31d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sr. Solutions Architect - Digital Native Business, Strategics</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NV, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=905e4e31b6a4eb13</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>QE Architect</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>NATIONMIND LLC</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf751a8cb9bbc437</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Software Architect – Manufacturing Test</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cerebras Systems</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Software Engineer II - MCP Development</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Kiewit Corporation</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Lenexa, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Contract Associate Development Engineer</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Sinclair Broadcast Group</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hunt Valley, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Backend Engineer/Data Engineer/Aspiring AI Generalist</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Wider Security LLC</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Newport, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da73b50279ff0b8d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-22.xlsx
+++ b/results/job_matches_2026-07-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer - 2378720</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.7</v>
+        <v>23.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf953a2c9ee5bf5</t>
+          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Orlando Utilities Commission</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.7</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, RDS, Azure, Data Factory, Databricks</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc6276c79dcfd60</t>
+          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2378720</t>
+          <t>Java Backend Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Otomeshan technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>21.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a79ad3ad8ee3cf8</t>
+          <t>https://www.indeed.com/viewjob?jk=05dceb327eaee169</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Orlando Utilities Commission</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Blob Storage, Google Cloud Platform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716f1c8a10b20d9b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Backend Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Otomeshan technology</t>
+          <t>Conduit services</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Azure, Databricks, GCP, Hadoop</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05dceb327eaee169</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1b649e399da37</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>University of Texas at Austin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f5e10429558c3d9</t>
+          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Conduit services</t>
+          <t>Niagara Bottling</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Diamond Bar, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1b649e399da37</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Texas at Austin</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Google Cloud Platform, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd667536ab6444e</t>
+          <t>https://www.indeed.com/viewjob?jk=4981bd5c543f4424</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Niagara Bottling</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Diamond Bar, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6929ba2eeed1b8</t>
+          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4981bd5c543f4424</t>
+          <t>https://www.indeed.com/viewjob?jk=1c4e902c4bf7accf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>TECHSTRA SOLUTIONS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Azure, Data Factory, Blob Storage</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95ed4554e9125c0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>AI Ops / DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a29827250f0150e</t>
+          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>DATA SCIENTIST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TECHSTRA SOLUTIONS</t>
+          <t>SANTEE COOPER</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Moncks Corner, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cb2faf83c978e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5384d191c57a074d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, DynamoDB, CI/CD, AWS CodePipeline</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,347 +951,347 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c4e902c4bf7accf</t>
+          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer (RICHMOND, VA, US, 23219)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Spark Streaming, Kafka, Kafka Connect, Snowflake</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b18ba5356fc564</t>
+          <t>https://www.indeed.com/viewjob?jk=87068c1cc4a7e538</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Ops / DevOps Engineer</t>
+          <t>Java Microservices Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7c47ddb67ad7812</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e170e5d541b6f7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DATA SCIENTIST</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANTEE COOPER</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Moncks Corner, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
+          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5384d191c57a074d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Associate ETL Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>Lincoln Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Spark, Scala, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9b00ff42cf98f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c3da01dbb88956</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87068c1cc4a7e538</t>
+          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Java Microservices Engineer</t>
+          <t>Senior Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Left Field Labs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5e170e5d541b6f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vision Radiology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Databricks, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, Azure, Event Hubs, BigQuery, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3fddfc784d8dfed</t>
+          <t>https://www.indeed.com/viewjob?jk=ea77e5dc301d8192</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate ETL Developer</t>
+          <t>Senior Analytics Engineer (AI Insurance SaaS)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lincoln Financial</t>
+          <t>EvolutionIQ</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hive, Scala, Snowflake, Oracle</t>
+          <t>Redshift, RDS, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c3da01dbb88956</t>
+          <t>https://www.indeed.com/viewjob?jk=c5f178ece3a91c11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Research Engineer II - ML Ops</t>
+          <t>Data Engineer (Backend Python Development)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Green Courte Residential Holdings</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Spark, Scala, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Polars, Snowflake, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cffd0794f9ae1f</t>
+          <t>https://www.indeed.com/viewjob?jk=8581636bcd3b21c7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Cloud and AI Ops Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97efab58cd263135</t>
+          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Left Field Labs</t>
+          <t>MedVet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MySQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e15a7800e885fb97</t>
+          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Data Engineer (HYBRID)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Texas Mutual Insurance Company</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6430dfa06f6062e</t>
+          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (HYBRID)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>LSEG (London Stock Exchange Group)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, Scala, DynamoDB, Dimensional Modeling</t>
+          <t>AWS, Lambda, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc72e4bf4365c113</t>
+          <t>https://www.indeed.com/viewjob?jk=3aada6e7b7a0a352</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (AI Insurance SaaS)</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EvolutionIQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5f178ece3a91c11</t>
+          <t>https://www.indeed.com/viewjob?jk=ba77f8c3e7eac143</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer (Backend Python Development)</t>
+          <t>Enterprise Integration Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Green Courte Residential Holdings</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,52 +1466,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Polars, Snowflake, dbt, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8581636bcd3b21c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud and AI Ops Engineer</t>
+          <t>AI Native, Tech Ops Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>ConsumerAffairs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, MongoDB, DynamoDB, NoSQL, Splunk, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45248088909a2e31</t>
+          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
         </is>
       </c>
     </row>
@@ -1523,55 +1523,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MedVet</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Dimension Tables</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaf547f655867771</t>
+          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>University Federal Credit Union</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,172 +1581,172 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aada6e7b7a0a352</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cfb563279695cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior AWS Developer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Oracle, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea3b78846f75e27</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>Software Developer II (Mid-level, Full-stack)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Science Systems and Applications, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524c59d936a754bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f769425f85072466</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer – CAD Infrastructure Team</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b12976fb7bd11e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Machine Learning Engineer (AI / ML: Python / Go)</t>
+          <t>Programmer Analyst III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Benzinga</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, Kafka, MLOps, MLflow</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a52f044b0c00d9c9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba77f8c3e7eac143</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Integration Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Snowflake, Oracle, SQL Server, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f999b434638c38c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Native, Tech Ops Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ConsumerAffairs</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04a08795fba7ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee377598f848d9cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (EKS/Kubernetes)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0028549706f10f55</t>
+          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University Federal Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,94 +1931,94 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cfb563279695cc</t>
+          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Neo4j</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d770528059fec1c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL, MySQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab41d77344b564f</t>
+          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>iSynergy Information Technologies</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21910689207bf63d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4665edec79f4e66b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Developer II (Mid-level, Full-stack)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Science Systems and Applications, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lanham, MD, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f769425f85072466</t>
+          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1520d3632771362e</t>
+          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Programmer Analyst III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d2473aefc906ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8574e7ed96b2d014</t>
+          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
+          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca85bb90457e515</t>
+          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e2bf1384f6dd310</t>
+          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56331cd42e8dcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb30216d9da276e2</t>
+          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733c0622e64f40ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342b4c677a915615</t>
+          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b70c9ad22f6254e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f76c3abbd4c553e4</t>
+          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2cbf2b08d1cb36b</t>
+          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d85b4eff6fe8e85</t>
+          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a24ce616bf5af5e</t>
+          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=434ed55692a471a2</t>
+          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbad99ad4589592</t>
+          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61295a0c9fc6fea5</t>
+          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ead77417d2729b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0821550bdf4c46c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc44f5c0ae67d880</t>
+          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cabcc636433c59</t>
+          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55c0812991c7213d</t>
+          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd9808ebf85c3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=738ca4292d8da7cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e60baa0699eba4</t>
+          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76666127e6d25ff8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4169168d1365af8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=336b4c2662ea6d10</t>
+          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=141982a00d6663d5</t>
+          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a61a6c3cb59a6cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7168135f559179c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abb882c8e0753077</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2eb41d81cf76d5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0490fa097f44f625</t>
+          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=beef9076c906f91c</t>
+          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48b29980cdd7361</t>
+          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5178a992a1ca9b84</t>
+          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f493fa38e54b75</t>
+          <t>https://www.indeed.com/viewjob?jk=21c9762fb6f0e415</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0068a8628378e3d8</t>
+          <t>https://www.indeed.com/viewjob?jk=08a0f24c148c6273</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bb4d10c31fddbb</t>
+          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae377a3594e9efb9</t>
+          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Solutions Architect - Financial Services (Fintech / Data Providers)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5377640e7dce30</t>
+          <t>https://www.indeed.com/viewjob?jk=cfda330d88e5394e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Microsoft Data &amp; AI Services Solution Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>MCAConnect</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>Azure, Event Hubs, Hadoop, Spark, Scala, Kafka, Dimensional Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60ed409aec255bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=f08ca180466ecf65</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Database Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=161aaba31e201a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>sssssss</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a11fb60e0f04716e</t>
+          <t>https://www.indeed.com/viewjob?jk=24dde647fb9dfea1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d70196db72cd4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1bef00d998ec50</t>
+          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63b24ea01ef2677</t>
+          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,15 +3838,15 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23e2d1a0f368fd1b</t>
+          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c62b6424dcc176cb</t>
+          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3908,15 +3908,15 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab79309367ff5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,15 +3943,15 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2683253095fc1283</t>
+          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python, Databricks</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Oracle, SQL Server, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e7dfe61ee7b587</t>
+          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – AI Applications</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mears Group Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, NoSQL, ETL, Power BI, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c131dea7fda0b9ad</t>
+          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Cloud Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08a0f24c148c6273</t>
+          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=306b6fefd175d426</t>
+          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Solutions Architect - Financial Services (Fintech / Data Providers)</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfda330d88e5394e</t>
+          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Microsoft Data &amp; AI Services Solution Architect</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MCAConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Hadoop, Spark, Scala, Kafka, Dimensional Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f08ca180466ecf65</t>
+          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Developer</t>
+          <t>Senior Full Stack Software Development Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Spark, PySpark, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43b6a924924be72b</t>
+          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95e34001e24f0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2860a0edb5db709</t>
+          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be89033e31f6b57</t>
+          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba399a49583ceef</t>
+          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911f341f66bc4d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b363d6a1469d11ee</t>
+          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13021fa5d76c1b76</t>
+          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7149b04d3f2801f5</t>
+          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98e758f85e9b562e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f87012f560dfe286</t>
+          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f5395469b7eaeb0</t>
+          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61dc24f567b820b9</t>
+          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff17d7210577ed32</t>
+          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85d4caff1e9ac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b96c9f6dd36e7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11534212ecc4e307</t>
+          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186c532699b21ec8</t>
+          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=917c83032f017295</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ccecf308b741f34</t>
+          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05a5ccb7686a7931</t>
+          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a49cf14a94b26f6</t>
+          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c7c4c01f867efc</t>
+          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b4f64cc2fc80a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ce5bce4e1c1fce</t>
+          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bc198fa423e2a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=483fbe310adf2296</t>
+          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e1b8f1a52596aad</t>
+          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffaa79ed7e7702a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494a700763f8ed79</t>
+          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e35609c5a789672a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=610cb96ac9a72d74</t>
+          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2ff5fb4c574fe8</t>
+          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6755a53e9eec6926</t>
+          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42cc610cc5ec7e2</t>
+          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c39a7da90b2dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,207 +5466,207 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071b3a91fd4d701d</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Master Data Management (MDM) Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>American Association of Insurance Services</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5cf09a541b33228</t>
+          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Data Engineer, Senior (Hybrid)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37fd68ce2edede72</t>
+          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4cb1818acbdee1</t>
+          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=106a3894b61c1364</t>
+          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c930b7942ef30177</t>
+          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>IT Solutions Architect III</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b54703b7a63ca495</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1b2254b13ddb4d</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Database Architect</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Tewksbury, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Redshift, Hadoop, Scala, DynamoDB, Cassandra, ETL, ELT, CloudWatch</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,67 +5711,67 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b2896dd4dfe7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=e937495306ed591b</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CalAmp</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1bb47749e3f3b80</t>
+          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,32 +5781,32 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3250523291990ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f34e5f97d02e5021</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,32 +5816,32 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feb5b54c9594f90e</t>
+          <t>https://www.indeed.com/viewjob?jk=853d0155af0fe88a</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,32 +5851,32 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df419d6da36aaf19</t>
+          <t>https://www.indeed.com/viewjob?jk=025149537375b19e</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Senior Software Engineer II- Streaming and Durability</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d7bfc0892e64c</t>
+          <t>https://www.indeed.com/viewjob?jk=2aaa5458d436295c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Development Engineer</t>
+          <t>Senior Software Engineer II - Streaming and Durability</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,32 +5921,32 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40345fd55a9efbda</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4086a87728e295</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Engineer II- Streaming and Durability</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0ea90716b5e5176</t>
+          <t>https://www.indeed.com/viewjob?jk=e37397e5a5a0fd15</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Master Data Management (MDM) Data Engineer</t>
+          <t>Data Engineer, Business Strategy &amp; Analytics</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>American Association of Insurance Services</t>
+          <t>Nashville Predators</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, Step Functions, S3, RDS, Scala, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b76ba73da353aba</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior (Hybrid)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac8907849bb6de65</t>
+          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD, Airflow</t>
+          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=407523eff2e48c9e</t>
+          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/PySpark/Databricks/AWS</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,147 +6086,147 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057666b67f419a52</t>
+          <t>https://www.indeed.com/viewjob?jk=b184430c41a2294c</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer I-II</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>United Power</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brighton, CO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4743ecd6e6d322f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d42cdf36323593a</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Streaming and Durability</t>
+          <t>Cloud Infrastructure/DevOps Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f34e5f97d02e5021</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Streaming and Durability</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Fooda</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853d0155af0fe88a</t>
+          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Streaming and Durability</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025149537375b19e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e3a8591136d286e</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II- Streaming and Durability</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,32 +6271,32 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2aaa5458d436295c</t>
+          <t>https://www.indeed.com/viewjob?jk=69be0bf694e2c4f3</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II - Streaming and Durability</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4086a87728e295</t>
+          <t>https://www.indeed.com/viewjob?jk=10660dc7b9459d79</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II- Streaming and Durability</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Kafka, PostgreSQL, DynamoDB, ETL, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37397e5a5a0fd15</t>
+          <t>https://www.indeed.com/viewjob?jk=81fada79a0fdb321</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IT Solutions Architect III</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,32 +6376,32 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1b2254b13ddb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4359bfbc2f710789</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Database Architect</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Tewksbury, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Hadoop, Scala, DynamoDB, Cassandra, ETL, ELT, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,234 +6411,234 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e937495306ed591b</t>
+          <t>https://www.indeed.com/viewjob?jk=993ef220ab5ba1b7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Forward Deployed Engineer-Retail</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CalAmp</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50e5d82f58dbed7</t>
+          <t>https://www.indeed.com/viewjob?jk=e3bec0ebeeca3759</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Solutions Architect - AI</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Kiewit Corporation</t>
+          <t>Five Below</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71ff5fe15d7d351d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae65b3d4f08cae09</t>
+          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer, Business Strategy &amp; Analytics</t>
+          <t>QE Architect</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Nashville Predators</t>
+          <t>NATIONMIND LLC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, PostgreSQL, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea74b45c1bfb0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=cf751a8cb9bbc437</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Risk-Salt Lake City-Associate-Software Engineering</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Marlboro, MA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>S3, HDFS, Spark, Scala, Dask, Snowflake, Tableau, Maven, Airflow, Apache Airflow</t>
+          <t>RDS, Databricks, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1772c65621fbfa6e</t>
+          <t>https://www.indeed.com/viewjob?jk=23d224fc86dd31d3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Solutions Architect - Digital Native Business, Strategics</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, PostgreSQL, ELT, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e1ec3a525992</t>
+          <t>https://www.indeed.com/viewjob?jk=905e4e31b6a4eb13</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Software Architect – Manufacturing Test</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cerebras Systems</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,14 +6656,14 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e3a8591136d286e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69be0bf694e2c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6ec4d249ca819f87</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10660dc7b9459d79</t>
+          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Software Engineer II - MCP Development</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kiewit Corporation</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fada79a0fdb321</t>
+          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
+          <t>Backend Engineer/Data Engineer/Aspiring AI Generalist</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Wider Security LLC</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Newport, RI, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6795,531 +6795,6 @@
         </is>
       </c>
       <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4359bfbc2f710789</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=993ef220ab5ba1b7</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer-Retail</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3bec0ebeeca3759</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Solutions Architect - AI</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Five Below</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1663c481c335933</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Sr. Consultant Machine Learning &amp; Knowledge Graph Engineer</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Dell Technologies</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>RDS, Spark, PySpark, Kafka, NoSQL, ETL, ELT, MLOps, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97f00350dc1cf2cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Cloud Infrastructure/DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f59c82228d31cc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Fooda</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, SQL Server, MySQL, Terraform, Kubernetes, Datadog</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d47b872c6cd26d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec4d249ca819f87</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Boston Scientific</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Marlboro, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Scala, Snowflake, MLOps, MLflow, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23d224fc86dd31d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Sr. Solutions Architect - Digital Native Business, Strategics</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>NV, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Kafka, ELT, MLflow</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=905e4e31b6a4eb13</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>QE Architect</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>NATIONMIND LLC</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf751a8cb9bbc437</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Software Architect – Manufacturing Test</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Cerebras Systems</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, CI/CD</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6bf1f8056f21747</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1eb4970ab969926f</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Software Engineer II - MCP Development</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Kiewit Corporation</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, SQL Server, CI/CD, Azure DevOps, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=466a34b0501dbfe6</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Contract Associate Development Engineer</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Sinclair Broadcast Group</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Hunt Valley, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c7da459b7e5a5519</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Backend Engineer/Data Engineer/Aspiring AI Generalist</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Wider Security LLC</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Newport, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=da73b50279ff0b8d</t>
         </is>
